--- a/healthcare_forms/038_daily_covid_19_pre_screening_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/038_daily_covid_19_pre_screening_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_medical_condition',_'label':_'no_medical_condition'}</t>
+          <t>no_medical_condition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No Medical Condition', 'label': 'No Medical Condition'}</t>
+          <t>No Medical Condition</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medical_condition_present',_'label':_'medical_condition_present'}</t>
+          <t>medical_condition_present</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medical Condition Present', 'label': 'Medical Condition Present'}</t>
+          <t>Medical Condition Present</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unknown_medical_condition',_'label':_'unknown_medical_condition'}</t>
+          <t>unknown_medical_condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Unknown Medical Condition', 'label': 'Unknown Medical Condition'}</t>
+          <t>Unknown Medical Condition</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'undecided',_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Undecided', 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fever',_'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fever', 'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chills',_'label':_'chills'}</t>
+          <t>chills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Chills', 'label': 'Chills'}</t>
+          <t>Chills</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'muscle',_'label':_'muscle'}</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Muscle', 'label': 'Muscle'}</t>
+          <t>Muscle</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fatigue',_'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Fatigue', 'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'headache',_'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Headache', 'label': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_blood_pressure',_'label':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High Blood Pressure', 'label': 'High Blood Pressure'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'diabetes',_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Diabetes', 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'vaccinated',_'label':_'vaccinated'}</t>
+          <t>vaccinated</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Vaccinated', 'label': 'Vaccinated'}</t>
+          <t>Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
